--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo_export.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0feature-3.0.4运营\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\product\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13065"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
   </bookViews>
   <sheets>
     <sheet name="总部或分支机构信息" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>销售机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,10 +34,6 @@
   </si>
   <si>
     <t>机构层级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -435,18 +431,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -461,29 +456,24 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerInstInfo_export.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\product\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0feature-3.0.4运营\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13065"/>
   </bookViews>
   <sheets>
     <sheet name="总部或分支机构信息" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>销售机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,6 +34,10 @@
   </si>
   <si>
     <t>机构层级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -431,17 +435,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -456,24 +461,29 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
